--- a/sampleprojects/TaxReturn/excel/states/NJ.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NJ.xlsx
@@ -347,268 +347,268 @@
     <t>(33 attributes)</t>
   </si>
   <si>
+    <t>nj_agi</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>NJ adjusted gross income (federal AGI as a simplification)</t>
+  </si>
+  <si>
+    <t>nj_bracket_1_limit_joint</t>
+  </si>
+  <si>
+    <t>20000.0</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>NJ bracket 1 upper limit joint ($0 - $20,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_1_limit_single</t>
+  </si>
+  <si>
+    <t>NJ bracket 1 upper limit single ($0 - $20,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_1_rate</t>
+  </si>
+  <si>
+    <t>0.014</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 1: 1.4% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_2_limit_joint</t>
+  </si>
+  <si>
+    <t>50000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 2 upper limit joint ($20,001 - $50,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_2_limit_single</t>
+  </si>
+  <si>
+    <t>35000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 2 upper limit single ($20,001 - $35,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_2_rate_joint</t>
+  </si>
+  <si>
+    <t>0.0175</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 2 joint: 1.75% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_2_rate_single</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 2 single: 1.75% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_3_limit_joint</t>
+  </si>
+  <si>
+    <t>70000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 3 upper limit joint ($50,001 - $70,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_3_limit_single</t>
+  </si>
+  <si>
+    <t>40000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 3 upper limit single ($35,001 - $40,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_3_rate_joint</t>
+  </si>
+  <si>
+    <t>0.0245</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 3 joint: 2.45% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_3_rate_single</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 3 single: 3.5% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_4_limit_joint</t>
+  </si>
+  <si>
+    <t>80000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 4 upper limit joint ($70,001 - $80,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_4_limit_single</t>
+  </si>
+  <si>
+    <t>75000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 4 upper limit single ($40,001 - $75,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_4_rate_joint</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 4 joint: 3.5% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_4_rate_single</t>
+  </si>
+  <si>
+    <t>0.05525</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 4 single: 5.525% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_5_limit_joint</t>
+  </si>
+  <si>
+    <t>150000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 5 upper limit joint ($80,001 - $150,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_5_limit_single</t>
+  </si>
+  <si>
+    <t>500000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 5 upper limit single ($75,001 - $500,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_5_rate_joint</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 5 joint: 5.525% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_5_rate_single</t>
+  </si>
+  <si>
+    <t>0.0637</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 5 single: 6.37% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_6_limit_joint</t>
+  </si>
+  <si>
+    <t>NJ bracket 6 upper limit joint ($150,001 - $500,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_6_limit_single</t>
+  </si>
+  <si>
+    <t>1000000.0</t>
+  </si>
+  <si>
+    <t>NJ bracket 6 upper limit single ($500,001 - $1,000,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_6_rate_joint</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 6 joint: 6.37% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_6_rate_single</t>
+  </si>
+  <si>
+    <t>0.0897</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 6 single: 8.97% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_7_limit_joint</t>
+  </si>
+  <si>
+    <t>NJ bracket 7 upper limit joint ($500,001 - $1,000,000)</t>
+  </si>
+  <si>
+    <t>nj_bracket_7_rate</t>
+  </si>
+  <si>
+    <t>0.1075</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 7: 10.75% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_7_rate_joint</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 7 joint: 8.97% (2025)</t>
+  </si>
+  <si>
+    <t>nj_bracket_8_rate_joint</t>
+  </si>
+  <si>
+    <t>NJ tax rate bracket 8 joint: 10.75% (2025)</t>
+  </si>
+  <si>
+    <t>nj_dependent_exemption</t>
+  </si>
+  <si>
+    <t>1500.0</t>
+  </si>
+  <si>
+    <t>NJ dependent exemption per dependent (2025)</t>
+  </si>
+  <si>
+    <t>nj_exemption_total</t>
+  </si>
+  <si>
+    <t>NJ total exemptions ($1,000/taxpayer + $1,500/dependent)</t>
+  </si>
+  <si>
+    <t>nj_personal_exemption</t>
+  </si>
+  <si>
+    <t>1000.0</t>
+  </si>
+  <si>
+    <t>NJ personal exemption (2025)</t>
+  </si>
+  <si>
     <t>nj_tax</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>rw</t>
-  </si>
-  <si>
     <t>NJ state income tax (computed)</t>
-  </si>
-  <si>
-    <t>nj_agi</t>
-  </si>
-  <si>
-    <t>NJ adjusted gross income (federal AGI as a simplification)</t>
-  </si>
-  <si>
-    <t>nj_bracket_1_limit_joint</t>
-  </si>
-  <si>
-    <t>20000.0</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>NJ bracket 1 upper limit joint ($0 - $20,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_1_limit_single</t>
-  </si>
-  <si>
-    <t>NJ bracket 1 upper limit single ($0 - $20,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_1_rate</t>
-  </si>
-  <si>
-    <t>0.014</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 1: 1.4% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_2_limit_joint</t>
-  </si>
-  <si>
-    <t>50000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 2 upper limit joint ($20,001 - $50,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_2_limit_single</t>
-  </si>
-  <si>
-    <t>35000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 2 upper limit single ($20,001 - $35,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_2_rate_joint</t>
-  </si>
-  <si>
-    <t>0.0175</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 2 joint: 1.75% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_2_rate_single</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 2 single: 1.75% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_3_limit_joint</t>
-  </si>
-  <si>
-    <t>70000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 3 upper limit joint ($50,001 - $70,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_3_limit_single</t>
-  </si>
-  <si>
-    <t>40000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 3 upper limit single ($35,001 - $40,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_3_rate_joint</t>
-  </si>
-  <si>
-    <t>0.0245</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 3 joint: 2.45% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_3_rate_single</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 3 single: 3.5% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_4_limit_joint</t>
-  </si>
-  <si>
-    <t>80000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 4 upper limit joint ($70,001 - $80,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_4_limit_single</t>
-  </si>
-  <si>
-    <t>75000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 4 upper limit single ($40,001 - $75,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_4_rate_joint</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 4 joint: 3.5% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_4_rate_single</t>
-  </si>
-  <si>
-    <t>0.05525</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 4 single: 5.525% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_5_limit_joint</t>
-  </si>
-  <si>
-    <t>150000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 5 upper limit joint ($80,001 - $150,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_5_limit_single</t>
-  </si>
-  <si>
-    <t>500000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 5 upper limit single ($75,001 - $500,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_5_rate_joint</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 5 joint: 5.525% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_5_rate_single</t>
-  </si>
-  <si>
-    <t>0.0637</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 5 single: 6.37% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_6_limit_joint</t>
-  </si>
-  <si>
-    <t>NJ bracket 6 upper limit joint ($150,001 - $500,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_6_limit_single</t>
-  </si>
-  <si>
-    <t>1000000.0</t>
-  </si>
-  <si>
-    <t>NJ bracket 6 upper limit single ($500,001 - $1,000,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_6_rate_joint</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 6 joint: 6.37% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_6_rate_single</t>
-  </si>
-  <si>
-    <t>0.0897</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 6 single: 8.97% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_7_limit_joint</t>
-  </si>
-  <si>
-    <t>NJ bracket 7 upper limit joint ($500,001 - $1,000,000)</t>
-  </si>
-  <si>
-    <t>nj_bracket_7_rate</t>
-  </si>
-  <si>
-    <t>0.1075</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 7: 10.75% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_7_rate_joint</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 7 joint: 8.97% (2025)</t>
-  </si>
-  <si>
-    <t>nj_bracket_8_rate_joint</t>
-  </si>
-  <si>
-    <t>NJ tax rate bracket 8 joint: 10.75% (2025)</t>
-  </si>
-  <si>
-    <t>nj_dependent_exemption</t>
-  </si>
-  <si>
-    <t>1500.0</t>
-  </si>
-  <si>
-    <t>NJ dependent exemption per dependent (2025)</t>
-  </si>
-  <si>
-    <t>nj_exemption_total</t>
-  </si>
-  <si>
-    <t>NJ total exemptions ($1,000/taxpayer + $1,500/dependent)</t>
-  </si>
-  <si>
-    <t>nj_personal_exemption</t>
-  </si>
-  <si>
-    <t>1000.0</t>
-  </si>
-  <si>
-    <t>NJ personal exemption (2025)</t>
   </si>
   <si>
     <t>nj_taxable_income</t>
@@ -4413,16 +4413,16 @@
         <v>15</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>15</v>
@@ -4445,7 +4445,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>110</v>
@@ -4454,13 +4454,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>119</v>
@@ -4495,16 +4495,16 @@
         <v>15</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>15</v>
@@ -4527,7 +4527,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>110</v>
@@ -4536,16 +4536,16 @@
         <v>15</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>15</v>
@@ -4568,7 +4568,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>110</v>
@@ -4577,16 +4577,16 @@
         <v>15</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>15</v>
@@ -4609,7 +4609,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>110</v>
@@ -4618,16 +4618,16 @@
         <v>15</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>15</v>
@@ -4650,7 +4650,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>110</v>
@@ -4659,13 +4659,13 @@
         <v>15</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>133</v>
@@ -4700,16 +4700,16 @@
         <v>15</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>15</v>
@@ -4732,7 +4732,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>110</v>
@@ -4741,16 +4741,16 @@
         <v>15</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>15</v>
@@ -4773,7 +4773,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>110</v>
@@ -4782,16 +4782,16 @@
         <v>15</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>15</v>
@@ -4814,7 +4814,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>110</v>
@@ -4823,16 +4823,16 @@
         <v>15</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>110</v>
@@ -4864,16 +4864,16 @@
         <v>15</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>15</v>
@@ -4896,7 +4896,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>110</v>
@@ -4905,16 +4905,16 @@
         <v>15</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>15</v>
@@ -4937,7 +4937,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>110</v>
@@ -4946,13 +4946,13 @@
         <v>15</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H18" s="16" t="s">
         <v>153</v>
@@ -4987,16 +4987,16 @@
         <v>15</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>15</v>
@@ -5019,7 +5019,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>110</v>
@@ -5028,16 +5028,16 @@
         <v>15</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>15</v>
@@ -5060,7 +5060,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>110</v>
@@ -5069,16 +5069,16 @@
         <v>15</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>15</v>
@@ -5101,7 +5101,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>110</v>
@@ -5110,13 +5110,13 @@
         <v>15</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>164</v>
@@ -5151,16 +5151,16 @@
         <v>15</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>15</v>
@@ -5183,7 +5183,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>110</v>
@@ -5192,13 +5192,13 @@
         <v>15</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H24" s="16" t="s">
         <v>169</v>
@@ -5233,16 +5233,16 @@
         <v>15</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>15</v>
@@ -5265,7 +5265,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>110</v>
@@ -5274,13 +5274,13 @@
         <v>15</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H26" s="16" t="s">
         <v>174</v>
@@ -5315,16 +5315,16 @@
         <v>15</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>15</v>
@@ -5347,7 +5347,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>110</v>
@@ -5356,13 +5356,13 @@
         <v>15</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H28" s="16" t="s">
         <v>179</v>
@@ -5397,16 +5397,16 @@
         <v>15</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>15</v>
@@ -5429,7 +5429,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>110</v>
@@ -5438,13 +5438,13 @@
         <v>15</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>184</v>
@@ -5479,13 +5479,13 @@
         <v>15</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H31" s="16" t="s">
         <v>186</v>
@@ -5520,16 +5520,16 @@
         <v>15</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>15</v>
@@ -5552,7 +5552,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>110</v>
@@ -5561,13 +5561,13 @@
         <v>15</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>191</v>
@@ -5602,16 +5602,16 @@
         <v>15</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>15</v>
@@ -5634,7 +5634,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>110</v>
@@ -5643,13 +5643,13 @@
         <v>15</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H35" s="16" t="s">
         <v>196</v>
